--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V317"/>
+  <dimension ref="A1:V318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23270,6 +23270,78 @@
       <c r="V317" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="C318" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="D318" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="E318" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="F318" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="G318" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="H318" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="I318" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="J318" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="K318" t="n">
+        <v>328.73</v>
+      </c>
+      <c r="L318" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="M318" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="N318" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="O318" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="P318" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>341.36</v>
+      </c>
+      <c r="R318" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="S318" t="n">
+        <v>336.52</v>
+      </c>
+      <c r="T318" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="U318" t="n">
+        <v>345.16</v>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23284,7 +23356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26487,6 +26559,16 @@
       </c>
       <c r="B320" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -26655,28 +26737,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4123354168769413</v>
+        <v>-0.4106775530617245</v>
       </c>
       <c r="J2" t="n">
+        <v>317</v>
+      </c>
+      <c r="K2" t="n">
         <v>316</v>
       </c>
-      <c r="K2" t="n">
-        <v>315</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2785177604300486</v>
+        <v>0.2780326949138131</v>
       </c>
       <c r="M2" t="n">
-        <v>3.681560187818941</v>
+        <v>3.678779940044576</v>
       </c>
       <c r="N2" t="n">
-        <v>24.08088937092635</v>
+        <v>24.02748484318844</v>
       </c>
       <c r="O2" t="n">
-        <v>4.907228277849559</v>
+        <v>4.901783842968642</v>
       </c>
       <c r="P2" t="n">
-        <v>372.675558809433</v>
+        <v>372.6584403982038</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26733,28 +26815,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3571296849992892</v>
+        <v>-0.3551752781815912</v>
       </c>
       <c r="J3" t="n">
+        <v>317</v>
+      </c>
+      <c r="K3" t="n">
         <v>316</v>
       </c>
-      <c r="K3" t="n">
-        <v>315</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1776529428335692</v>
+        <v>0.1768701235911245</v>
       </c>
       <c r="M3" t="n">
-        <v>4.49748578615824</v>
+        <v>4.494206608948447</v>
       </c>
       <c r="N3" t="n">
-        <v>32.27997066241313</v>
+        <v>32.20950596915716</v>
       </c>
       <c r="O3" t="n">
-        <v>5.681546502706206</v>
+        <v>5.675341925307864</v>
       </c>
       <c r="P3" t="n">
-        <v>358.3934098519111</v>
+        <v>358.3732294611532</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26811,28 +26893,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4210499088472461</v>
+        <v>-0.4192391838545401</v>
       </c>
       <c r="J4" t="n">
+        <v>317</v>
+      </c>
+      <c r="K4" t="n">
         <v>316</v>
       </c>
-      <c r="K4" t="n">
-        <v>315</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2279485852694861</v>
+        <v>0.2274459012436312</v>
       </c>
       <c r="M4" t="n">
-        <v>4.371265644342866</v>
+        <v>4.366643122503364</v>
       </c>
       <c r="N4" t="n">
-        <v>32.83030902088117</v>
+        <v>32.75361493756486</v>
       </c>
       <c r="O4" t="n">
-        <v>5.729773906611078</v>
+        <v>5.723077400976232</v>
       </c>
       <c r="P4" t="n">
-        <v>358.9674197667581</v>
+        <v>358.9487229746791</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26889,28 +26971,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4564054867246459</v>
+        <v>-0.455607327004725</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2245253539884682</v>
+        <v>0.2250391233034761</v>
       </c>
       <c r="M5" t="n">
-        <v>4.94799263857651</v>
+        <v>4.936540927831267</v>
       </c>
       <c r="N5" t="n">
-        <v>39.33107502493356</v>
+        <v>39.21150467982574</v>
       </c>
       <c r="O5" t="n">
-        <v>6.271449196552067</v>
+        <v>6.261909028389485</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8643967238027</v>
+        <v>366.8561446329979</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26967,28 +27049,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3701627834753254</v>
+        <v>-0.3688258978494097</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1911535889812322</v>
+        <v>0.1909801738344601</v>
       </c>
       <c r="M6" t="n">
-        <v>4.483367418875806</v>
+        <v>4.475381578741588</v>
       </c>
       <c r="N6" t="n">
-        <v>31.69574768316982</v>
+        <v>31.60996790045916</v>
       </c>
       <c r="O6" t="n">
-        <v>5.629897661873599</v>
+        <v>5.622274264073139</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2424454783833</v>
+        <v>362.2286235561473</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27045,28 +27127,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4024995126902638</v>
+        <v>-0.4002551866005021</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1080456768225956</v>
+        <v>0.1075496719277755</v>
       </c>
       <c r="M7" t="n">
-        <v>6.489552347711129</v>
+        <v>6.483210180125847</v>
       </c>
       <c r="N7" t="n">
-        <v>72.91316799442831</v>
+        <v>72.72478067830858</v>
       </c>
       <c r="O7" t="n">
-        <v>8.538920774572645</v>
+        <v>8.527882543651065</v>
       </c>
       <c r="P7" t="n">
-        <v>342.2128718734486</v>
+        <v>342.1896727344313</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27123,28 +27205,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4689068112111514</v>
+        <v>-0.4678883765091636</v>
       </c>
       <c r="J8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.209487775515513</v>
+        <v>0.2098290871242244</v>
       </c>
       <c r="M8" t="n">
-        <v>5.021815234076664</v>
+        <v>5.011336903021229</v>
       </c>
       <c r="N8" t="n">
-        <v>45.23379417591651</v>
+        <v>45.09967168037904</v>
       </c>
       <c r="O8" t="n">
-        <v>6.725607346248851</v>
+        <v>6.715628911753466</v>
       </c>
       <c r="P8" t="n">
-        <v>339.069031474297</v>
+        <v>339.058504123419</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27201,28 +27283,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4878845714006614</v>
+        <v>-0.4860455826940533</v>
       </c>
       <c r="J9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2481875550651823</v>
+        <v>0.2478765796997903</v>
       </c>
       <c r="M9" t="n">
-        <v>4.792310338582009</v>
+        <v>4.786130211389429</v>
       </c>
       <c r="N9" t="n">
-        <v>39.31006016594139</v>
+        <v>39.2139994461637</v>
       </c>
       <c r="O9" t="n">
-        <v>6.269773533863994</v>
+        <v>6.262108226960286</v>
       </c>
       <c r="P9" t="n">
-        <v>341.956085774603</v>
+        <v>341.937076525078</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27279,28 +27361,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5549004952021569</v>
+        <v>-0.5527919613910627</v>
       </c>
       <c r="J10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3205341268854038</v>
+        <v>0.3200876306222145</v>
       </c>
       <c r="M10" t="n">
-        <v>4.623907697937771</v>
+        <v>4.62101972447745</v>
       </c>
       <c r="N10" t="n">
-        <v>35.58472618267122</v>
+        <v>35.50920984127082</v>
       </c>
       <c r="O10" t="n">
-        <v>5.965293469953613</v>
+        <v>5.958960466496721</v>
       </c>
       <c r="P10" t="n">
-        <v>345.9159695320905</v>
+        <v>345.8941740500394</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27357,28 +27439,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6708195568823709</v>
+        <v>-0.670962134509225</v>
       </c>
       <c r="J11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4611001247087607</v>
+        <v>0.4628443772939757</v>
       </c>
       <c r="M11" t="n">
-        <v>4.030681190084947</v>
+        <v>4.01867586918581</v>
       </c>
       <c r="N11" t="n">
-        <v>28.67241700154343</v>
+        <v>28.58213571782499</v>
       </c>
       <c r="O11" t="n">
-        <v>5.354663108127665</v>
+        <v>5.346226306267346</v>
       </c>
       <c r="P11" t="n">
-        <v>346.4875783991291</v>
+        <v>346.4890521948495</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27435,28 +27517,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7002069021576003</v>
+        <v>-0.6997368141726066</v>
       </c>
       <c r="J12" t="n">
+        <v>317</v>
+      </c>
+      <c r="K12" t="n">
         <v>316</v>
       </c>
-      <c r="K12" t="n">
-        <v>315</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.4600138520232857</v>
+        <v>0.4613080270493291</v>
       </c>
       <c r="M12" t="n">
-        <v>4.309352780264435</v>
+        <v>4.298220116952723</v>
       </c>
       <c r="N12" t="n">
-        <v>31.18360508133695</v>
+        <v>31.08673434130815</v>
       </c>
       <c r="O12" t="n">
-        <v>5.584228244022351</v>
+        <v>5.5755478960644</v>
       </c>
       <c r="P12" t="n">
-        <v>350.7861259870351</v>
+        <v>350.7812421630268</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27513,28 +27595,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7229117437727582</v>
+        <v>-0.7212996462893062</v>
       </c>
       <c r="J13" t="n">
+        <v>317</v>
+      </c>
+      <c r="K13" t="n">
         <v>316</v>
       </c>
-      <c r="K13" t="n">
-        <v>315</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.441881725057882</v>
+        <v>0.4422635275326299</v>
       </c>
       <c r="M13" t="n">
-        <v>4.688701462065261</v>
+        <v>4.681020118023987</v>
       </c>
       <c r="N13" t="n">
-        <v>35.76453637283867</v>
+        <v>35.67266217432312</v>
       </c>
       <c r="O13" t="n">
-        <v>5.980345840571318</v>
+        <v>5.972659556204683</v>
       </c>
       <c r="P13" t="n">
-        <v>349.1137625233299</v>
+        <v>349.0970141684585</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27591,28 +27673,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6971874315858974</v>
+        <v>-0.6940070246546908</v>
       </c>
       <c r="J14" t="n">
+        <v>317</v>
+      </c>
+      <c r="K14" t="n">
         <v>316</v>
       </c>
-      <c r="K14" t="n">
-        <v>315</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.4605813799808228</v>
+        <v>0.4592829657115465</v>
       </c>
       <c r="M14" t="n">
-        <v>4.276976055399635</v>
+        <v>4.278348474236825</v>
       </c>
       <c r="N14" t="n">
-        <v>30.84469589725835</v>
+        <v>30.83000594712302</v>
       </c>
       <c r="O14" t="n">
-        <v>5.553800131194707</v>
+        <v>5.552477460298513</v>
       </c>
       <c r="P14" t="n">
-        <v>342.1807369233106</v>
+        <v>342.1476951349162</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27669,28 +27751,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6691821153105167</v>
+        <v>-0.664472115868037</v>
       </c>
       <c r="J15" t="n">
+        <v>317</v>
+      </c>
+      <c r="K15" t="n">
         <v>316</v>
       </c>
-      <c r="K15" t="n">
-        <v>315</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.4374650847793565</v>
+        <v>0.4341834321583754</v>
       </c>
       <c r="M15" t="n">
-        <v>4.398172436342112</v>
+        <v>4.411088735849972</v>
       </c>
       <c r="N15" t="n">
-        <v>31.20014229014685</v>
+        <v>31.28326667201079</v>
       </c>
       <c r="O15" t="n">
-        <v>5.585708754504378</v>
+        <v>5.593144613901091</v>
       </c>
       <c r="P15" t="n">
-        <v>337.026443109497</v>
+        <v>336.9775101244161</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27747,28 +27829,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6509153588430382</v>
+        <v>-0.644755677891497</v>
       </c>
       <c r="J16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3885610657918951</v>
+        <v>0.3835757427075221</v>
       </c>
       <c r="M16" t="n">
-        <v>4.81457120217565</v>
+        <v>4.830995997481293</v>
       </c>
       <c r="N16" t="n">
-        <v>36.34819725394894</v>
+        <v>36.54706087325379</v>
       </c>
       <c r="O16" t="n">
-        <v>6.02894661229878</v>
+        <v>6.045416517763998</v>
       </c>
       <c r="P16" t="n">
-        <v>344.6717674655031</v>
+        <v>344.608096105379</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27825,28 +27907,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.437795470269673</v>
+        <v>-0.4322980203500149</v>
       </c>
       <c r="J17" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K17" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2253507490555406</v>
+        <v>0.2209089065459914</v>
       </c>
       <c r="M17" t="n">
-        <v>4.822414674649069</v>
+        <v>4.837999038254741</v>
       </c>
       <c r="N17" t="n">
-        <v>35.91936552861682</v>
+        <v>36.05579094582141</v>
       </c>
       <c r="O17" t="n">
-        <v>5.993276693814229</v>
+        <v>6.004647445589242</v>
       </c>
       <c r="P17" t="n">
-        <v>343.8542734239767</v>
+        <v>343.7974474103647</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27903,28 +27985,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4608375974189</v>
+        <v>-0.4552399441992251</v>
       </c>
       <c r="J18" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K18" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2766908086078991</v>
+        <v>0.2714407713304187</v>
       </c>
       <c r="M18" t="n">
-        <v>4.440409920265957</v>
+        <v>4.458179695050054</v>
       </c>
       <c r="N18" t="n">
-        <v>30.26670116864442</v>
+        <v>30.43014528702954</v>
       </c>
       <c r="O18" t="n">
-        <v>5.501518078552903</v>
+        <v>5.516352534694419</v>
       </c>
       <c r="P18" t="n">
-        <v>341.8733945734478</v>
+        <v>341.8155327788511</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27981,28 +28063,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5260127699493756</v>
+        <v>-0.5213136024191214</v>
       </c>
       <c r="J19" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K19" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4210617716259201</v>
+        <v>0.416161193348846</v>
       </c>
       <c r="M19" t="n">
-        <v>3.608220143870341</v>
+        <v>3.62199362573172</v>
       </c>
       <c r="N19" t="n">
-        <v>20.74049033679236</v>
+        <v>20.85753648672113</v>
       </c>
       <c r="O19" t="n">
-        <v>4.554172848804968</v>
+        <v>4.567005198893596</v>
       </c>
       <c r="P19" t="n">
-        <v>342.6177228847927</v>
+        <v>342.5691485527037</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28059,28 +28141,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3682233135924869</v>
+        <v>-0.3660842391399339</v>
       </c>
       <c r="J20" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K20" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L20" t="n">
-        <v>0.257873779168308</v>
+        <v>0.2565678624544141</v>
       </c>
       <c r="M20" t="n">
-        <v>3.726775045750969</v>
+        <v>3.725409430695188</v>
       </c>
       <c r="N20" t="n">
-        <v>21.27321773140725</v>
+        <v>21.24392006962153</v>
       </c>
       <c r="O20" t="n">
-        <v>4.612289857696202</v>
+        <v>4.609112720429121</v>
       </c>
       <c r="P20" t="n">
-        <v>349.5141287915578</v>
+        <v>349.4920176171526</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28137,28 +28219,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1822066082044841</v>
+        <v>-0.1825208249105321</v>
       </c>
       <c r="J21" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K21" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06248530089356086</v>
+        <v>0.06307452743290365</v>
       </c>
       <c r="M21" t="n">
-        <v>3.922597756538214</v>
+        <v>3.9113017186285</v>
       </c>
       <c r="N21" t="n">
-        <v>27.15616868599319</v>
+        <v>27.07131840059839</v>
       </c>
       <c r="O21" t="n">
-        <v>5.211158094511544</v>
+        <v>5.203010513212365</v>
       </c>
       <c r="P21" t="n">
-        <v>350.4306811632009</v>
+        <v>350.4339291569208</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28196,7 +28278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V317"/>
+  <dimension ref="A1:V318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63659,6 +63741,118 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-41.317433983626316,175.86271792652352</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-41.31790259740666,175.86205079080923</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-41.3183998419458,175.8614412698343</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-41.318902794605485,175.86084837951788</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-41.31942079059024,175.86027800788958</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-41.31977533911982,175.85948279449516</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-41.32015049536685,175.85874258283476</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-41.3205918707955,175.8580758546574</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-41.3209877751955,175.85736445702307</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-41.321282331800305,175.85657596074893</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-41.3215875014452,175.8557976744265</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-41.32183497184242,175.85496577369264</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-41.32205602421026,175.8541148886271</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-41.32228816490007,175.85328682965547</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-41.322557722207435,175.85246465576142</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-41.322842346901986,175.85163927594263</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>-41.32315796604731,175.85083328387032</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>-41.32350243778427,175.85006234632533</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>-41.32387584689355,175.84931433658636</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>-41.32426367050154,175.84858025995905</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V318"/>
+  <dimension ref="A1:V320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23340,6 +23340,150 @@
         <v>345.16</v>
       </c>
       <c r="V318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="C319" t="n">
+        <v>352.08</v>
+      </c>
+      <c r="D319" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="E319" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="F319" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="G319" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="H319" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="I319" t="n">
+        <v>330.42</v>
+      </c>
+      <c r="J319" t="n">
+        <v>334.24</v>
+      </c>
+      <c r="K319" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="L319" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="M319" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="N319" t="n">
+        <v>331.87</v>
+      </c>
+      <c r="O319" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="P319" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="R319" t="n">
+        <v>338.39</v>
+      </c>
+      <c r="S319" t="n">
+        <v>336.55</v>
+      </c>
+      <c r="T319" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="U319" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="C320" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="D320" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="E320" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="F320" t="n">
+        <v>354.56</v>
+      </c>
+      <c r="G320" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="H320" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="I320" t="n">
+        <v>330.26</v>
+      </c>
+      <c r="J320" t="n">
+        <v>333.94</v>
+      </c>
+      <c r="K320" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="L320" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="M320" t="n">
+        <v>333.51</v>
+      </c>
+      <c r="N320" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="O320" t="n">
+        <v>329</v>
+      </c>
+      <c r="P320" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="R320" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="S320" t="n">
+        <v>336.36</v>
+      </c>
+      <c r="T320" t="n">
+        <v>343.02</v>
+      </c>
+      <c r="U320" t="n">
+        <v>344.67</v>
+      </c>
+      <c r="V320" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23356,7 +23500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26569,6 +26713,26 @@
       </c>
       <c r="B321" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -26737,28 +26901,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4106775530617245</v>
+        <v>-0.4087021029924899</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2780326949138131</v>
+        <v>0.2785748946176739</v>
       </c>
       <c r="M2" t="n">
-        <v>3.678779940044576</v>
+        <v>3.66616514454332</v>
       </c>
       <c r="N2" t="n">
-        <v>24.02748484318844</v>
+        <v>23.89486890104848</v>
       </c>
       <c r="O2" t="n">
-        <v>4.901783842968642</v>
+        <v>4.888237811425348</v>
       </c>
       <c r="P2" t="n">
-        <v>372.6584403982038</v>
+        <v>372.6379738599701</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26815,28 +26979,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3551752781815912</v>
+        <v>-0.3521598525542254</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1768701235911245</v>
+        <v>0.1761177358846479</v>
       </c>
       <c r="M3" t="n">
-        <v>4.494206608948447</v>
+        <v>4.482700070684224</v>
       </c>
       <c r="N3" t="n">
-        <v>32.20950596915716</v>
+        <v>32.04670462973792</v>
       </c>
       <c r="O3" t="n">
-        <v>5.675341925307864</v>
+        <v>5.660980889363426</v>
       </c>
       <c r="P3" t="n">
-        <v>358.3732294611532</v>
+        <v>358.341985910249</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26893,28 +27057,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4192391838545401</v>
+        <v>-0.4161993869436146</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2274459012436312</v>
+        <v>0.2269776299467762</v>
       </c>
       <c r="M4" t="n">
-        <v>4.366643122503364</v>
+        <v>4.354583054569225</v>
       </c>
       <c r="N4" t="n">
-        <v>32.75361493756486</v>
+        <v>32.58768487458389</v>
       </c>
       <c r="O4" t="n">
-        <v>5.723077400976232</v>
+        <v>5.708562417507922</v>
       </c>
       <c r="P4" t="n">
-        <v>358.9487229746791</v>
+        <v>358.9172265465426</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26971,28 +27135,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.455607327004725</v>
+        <v>-0.4537958145412414</v>
       </c>
       <c r="J5" t="n">
+        <v>319</v>
+      </c>
+      <c r="K5" t="n">
         <v>317</v>
       </c>
-      <c r="K5" t="n">
-        <v>315</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2250391233034761</v>
+        <v>0.2258718282281557</v>
       </c>
       <c r="M5" t="n">
-        <v>4.936540927831267</v>
+        <v>4.914926402742555</v>
       </c>
       <c r="N5" t="n">
-        <v>39.21150467982574</v>
+        <v>38.97837463836142</v>
       </c>
       <c r="O5" t="n">
-        <v>6.261909028389485</v>
+        <v>6.243266343698739</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8561446329979</v>
+        <v>366.8373505350523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27049,28 +27213,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3688258978494097</v>
+        <v>-0.3660876078243985</v>
       </c>
       <c r="J6" t="n">
+        <v>319</v>
+      </c>
+      <c r="K6" t="n">
         <v>317</v>
       </c>
-      <c r="K6" t="n">
-        <v>315</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1909801738344601</v>
+        <v>0.1905457870310291</v>
       </c>
       <c r="M6" t="n">
-        <v>4.475381578741588</v>
+        <v>4.459819191987655</v>
       </c>
       <c r="N6" t="n">
-        <v>31.60996790045916</v>
+        <v>31.44234591424918</v>
       </c>
       <c r="O6" t="n">
-        <v>5.622274264073139</v>
+        <v>5.607347493623807</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2286235561473</v>
+        <v>362.2002131579635</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27127,28 +27291,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4002551866005021</v>
+        <v>-0.3957141222148187</v>
       </c>
       <c r="J7" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1075496719277755</v>
+        <v>0.1065095932813781</v>
       </c>
       <c r="M7" t="n">
-        <v>6.483210180125847</v>
+        <v>6.470816841588502</v>
       </c>
       <c r="N7" t="n">
-        <v>72.72478067830858</v>
+        <v>72.35510447264319</v>
       </c>
       <c r="O7" t="n">
-        <v>8.527882543651065</v>
+        <v>8.506180369157663</v>
       </c>
       <c r="P7" t="n">
-        <v>342.1896727344313</v>
+        <v>342.1425648384544</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27205,28 +27369,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4678883765091636</v>
+        <v>-0.4682343323042785</v>
       </c>
       <c r="J8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2098290871242244</v>
+        <v>0.2122583308056859</v>
       </c>
       <c r="M8" t="n">
-        <v>5.011336903021229</v>
+        <v>4.98162307394241</v>
       </c>
       <c r="N8" t="n">
-        <v>45.09967168037904</v>
+        <v>44.81779553415115</v>
       </c>
       <c r="O8" t="n">
-        <v>6.715628911753466</v>
+        <v>6.694609438507309</v>
       </c>
       <c r="P8" t="n">
-        <v>339.058504123419</v>
+        <v>339.0620944569427</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27283,28 +27447,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4860455826940533</v>
+        <v>-0.4846561691678869</v>
       </c>
       <c r="J9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2478765796997903</v>
+        <v>0.24922105104211</v>
       </c>
       <c r="M9" t="n">
-        <v>4.786130211389429</v>
+        <v>4.762777149803229</v>
       </c>
       <c r="N9" t="n">
-        <v>39.2139994461637</v>
+        <v>38.97622397381933</v>
       </c>
       <c r="O9" t="n">
-        <v>6.262108226960286</v>
+        <v>6.243094102592026</v>
       </c>
       <c r="P9" t="n">
-        <v>341.937076525078</v>
+        <v>341.9226640345972</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27361,28 +27525,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5527919613910627</v>
+        <v>-0.5495331941798439</v>
       </c>
       <c r="J10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3200876306222145</v>
+        <v>0.3200982505498129</v>
       </c>
       <c r="M10" t="n">
-        <v>4.62101972447745</v>
+        <v>4.609878776603284</v>
       </c>
       <c r="N10" t="n">
-        <v>35.50920984127082</v>
+        <v>35.33097543352452</v>
       </c>
       <c r="O10" t="n">
-        <v>5.958960466496721</v>
+        <v>5.943986493383419</v>
       </c>
       <c r="P10" t="n">
-        <v>345.8941740500394</v>
+        <v>345.8603704371085</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27439,28 +27603,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.670962134509225</v>
+        <v>-0.6686141369124627</v>
       </c>
       <c r="J11" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K11" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4628443772939757</v>
+        <v>0.4641593380849579</v>
       </c>
       <c r="M11" t="n">
-        <v>4.01867586918581</v>
+        <v>4.005880741797411</v>
       </c>
       <c r="N11" t="n">
-        <v>28.58213571782499</v>
+        <v>28.42657866118008</v>
       </c>
       <c r="O11" t="n">
-        <v>5.346226306267346</v>
+        <v>5.331658153068338</v>
       </c>
       <c r="P11" t="n">
-        <v>346.4890521948495</v>
+        <v>346.4646933217514</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27517,28 +27681,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6997368141726066</v>
+        <v>-0.6956569587121382</v>
       </c>
       <c r="J12" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K12" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4613080270493291</v>
+        <v>0.4611177176906078</v>
       </c>
       <c r="M12" t="n">
-        <v>4.298220116952723</v>
+        <v>4.292962258028635</v>
       </c>
       <c r="N12" t="n">
-        <v>31.08673434130815</v>
+        <v>30.96004973777384</v>
       </c>
       <c r="O12" t="n">
-        <v>5.5755478960644</v>
+        <v>5.564175566764033</v>
       </c>
       <c r="P12" t="n">
-        <v>350.7812421630268</v>
+        <v>350.7387058730563</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27595,28 +27759,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7212996462893062</v>
+        <v>-0.7172803006185129</v>
       </c>
       <c r="J13" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K13" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4422635275326299</v>
+        <v>0.4422873674958245</v>
       </c>
       <c r="M13" t="n">
-        <v>4.681020118023987</v>
+        <v>4.669852955645416</v>
       </c>
       <c r="N13" t="n">
-        <v>35.67266217432312</v>
+        <v>35.51509987157508</v>
       </c>
       <c r="O13" t="n">
-        <v>5.972659556204683</v>
+        <v>5.959454662263576</v>
       </c>
       <c r="P13" t="n">
-        <v>349.0970141684585</v>
+        <v>349.055108855293</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27673,28 +27837,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6940070246546908</v>
+        <v>-0.6846901673411186</v>
       </c>
       <c r="J14" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K14" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4592829657115465</v>
+        <v>0.4529479139772098</v>
       </c>
       <c r="M14" t="n">
-        <v>4.278348474236825</v>
+        <v>4.294860091890786</v>
       </c>
       <c r="N14" t="n">
-        <v>30.83000594712302</v>
+        <v>30.99544555915205</v>
       </c>
       <c r="O14" t="n">
-        <v>5.552477460298513</v>
+        <v>5.567355346944548</v>
       </c>
       <c r="P14" t="n">
-        <v>342.1476951349162</v>
+        <v>342.0505607978147</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27751,28 +27915,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.664472115868037</v>
+        <v>-0.6529983859675905</v>
       </c>
       <c r="J15" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K15" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4341834321583754</v>
+        <v>0.4246189665934595</v>
       </c>
       <c r="M15" t="n">
-        <v>4.411088735849972</v>
+        <v>4.448579665171581</v>
       </c>
       <c r="N15" t="n">
-        <v>31.28326667201079</v>
+        <v>31.63076207537637</v>
       </c>
       <c r="O15" t="n">
-        <v>5.593144613901091</v>
+        <v>5.624123227257416</v>
       </c>
       <c r="P15" t="n">
-        <v>336.9775101244161</v>
+        <v>336.8578864976253</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27829,28 +27993,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.644755677891497</v>
+        <v>-0.6336580659119218</v>
       </c>
       <c r="J16" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K16" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3835757427075221</v>
+        <v>0.375185595541109</v>
       </c>
       <c r="M16" t="n">
-        <v>4.830995997481293</v>
+        <v>4.858205188167409</v>
       </c>
       <c r="N16" t="n">
-        <v>36.54706087325379</v>
+        <v>36.83152659951168</v>
       </c>
       <c r="O16" t="n">
-        <v>6.045416517763998</v>
+        <v>6.068898301958246</v>
       </c>
       <c r="P16" t="n">
-        <v>344.608096105379</v>
+        <v>344.4929742889011</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27907,28 +28071,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4322980203500149</v>
+        <v>-0.4220047551755315</v>
       </c>
       <c r="J17" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K17" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2209089065459914</v>
+        <v>0.2128732003756595</v>
       </c>
       <c r="M17" t="n">
-        <v>4.837999038254741</v>
+        <v>4.8660116170681</v>
       </c>
       <c r="N17" t="n">
-        <v>36.05579094582141</v>
+        <v>36.27131551306766</v>
       </c>
       <c r="O17" t="n">
-        <v>6.004647445589242</v>
+        <v>6.022567186264315</v>
       </c>
       <c r="P17" t="n">
-        <v>343.7974474103647</v>
+        <v>343.6906716247066</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27985,28 +28149,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4552399441992251</v>
+        <v>-0.4451733769800077</v>
       </c>
       <c r="J18" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K18" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2714407713304187</v>
+        <v>0.2625428649064483</v>
       </c>
       <c r="M18" t="n">
-        <v>4.458179695050054</v>
+        <v>4.486846696711054</v>
       </c>
       <c r="N18" t="n">
-        <v>30.43014528702954</v>
+        <v>30.6619547225969</v>
       </c>
       <c r="O18" t="n">
-        <v>5.516352534694419</v>
+        <v>5.537323787047034</v>
       </c>
       <c r="P18" t="n">
-        <v>341.8155327788511</v>
+        <v>341.7111094308701</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28063,28 +28227,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5213136024191214</v>
+        <v>-0.5121478258666962</v>
       </c>
       <c r="J19" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K19" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L19" t="n">
-        <v>0.416161193348846</v>
+        <v>0.4066936863817341</v>
       </c>
       <c r="M19" t="n">
-        <v>3.62199362573172</v>
+        <v>3.648159313049333</v>
       </c>
       <c r="N19" t="n">
-        <v>20.85753648672113</v>
+        <v>21.07691841457367</v>
       </c>
       <c r="O19" t="n">
-        <v>4.567005198893596</v>
+        <v>4.590960511110248</v>
       </c>
       <c r="P19" t="n">
-        <v>342.5691485527037</v>
+        <v>342.4740686767697</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28141,28 +28305,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3660842391399339</v>
+        <v>-0.3621712367854275</v>
       </c>
       <c r="J20" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K20" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2565678624544141</v>
+        <v>0.2544027764558996</v>
       </c>
       <c r="M20" t="n">
-        <v>3.725409430695188</v>
+        <v>3.72081246565137</v>
       </c>
       <c r="N20" t="n">
-        <v>21.24392006962153</v>
+        <v>21.17460199158883</v>
       </c>
       <c r="O20" t="n">
-        <v>4.609112720429121</v>
+        <v>4.601586899276035</v>
       </c>
       <c r="P20" t="n">
-        <v>349.4920176171526</v>
+        <v>349.4514270447312</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28219,28 +28383,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1825208249105321</v>
+        <v>-0.1833927646987624</v>
       </c>
       <c r="J21" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K21" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06307452743290365</v>
+        <v>0.06441907304587469</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9113017186285</v>
+        <v>3.88971902625606</v>
       </c>
       <c r="N21" t="n">
-        <v>27.07131840059839</v>
+        <v>26.90519795551004</v>
       </c>
       <c r="O21" t="n">
-        <v>5.203010513212365</v>
+        <v>5.187022070081256</v>
       </c>
       <c r="P21" t="n">
-        <v>350.4339291569208</v>
+        <v>350.4429758574515</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28278,7 +28442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V318"/>
+  <dimension ref="A1:V320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63853,6 +64017,230 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-41.317431368867,175.86271321506794</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-41.31790170308665,175.86204929341457</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-41.31840002381515,175.8614415346075</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-41.318905495028396,175.86085254303697</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-41.319422715364304,175.86028100895575</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-41.31977435906376,175.85948156257075</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-41.320138731794344,175.8587294151869</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-41.3205792008744,175.85806284492247</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-41.32098322653953,175.857360377342</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-41.32129644508856,175.8565862722112</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-41.32160793849731,175.8558098818367</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-41.321840101420584,175.85496869003518</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-41.322078859178326,175.8541278709113</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-41.322302966987316,175.8532939778445</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-41.322548588853806,175.8524602382731</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>-41.32283970075016,175.8516374856091</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>-41.32315378208098,175.85082977305603</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>-41.32350266734832,175.85006253496965</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>-41.32387470665112,175.84931337732098</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>-41.32426396507493,175.84858053461352</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-41.31742507209879,175.86270186911523</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-41.317895778216126,175.86203937317597</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-41.318394264618625,175.86143315012404</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-41.3189020901473,175.8608472933825</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-41.31941974071344,175.8602763709445</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-41.31977742990601,175.85948542260073</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-41.32013529215295,175.8587255649984</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-41.32057806200501,175.85806167550834</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-41.320980989495546,175.85735837094168</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-41.32130149118018,175.85658995899212</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-41.32160867718591,175.85581032306857</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-41.32184059783136,175.8549689722619</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-41.32207422599655,175.85412523682388</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-41.32230372823749,175.85329434546574</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-41.3225527326902,175.85246224250375</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>-41.322838257394615,175.8516365090636</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>-41.323150434907824,175.85082696440492</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>-41.323501213442576,175.85006134022228</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>-41.32387318632786,175.84931209830052</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>-41.32426006197735,175.84857689544233</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V320"/>
+  <dimension ref="A1:V321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23486,6 +23486,78 @@
       <c r="V320" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>367</v>
+      </c>
+      <c r="C321" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="D321" t="n">
+        <v>354.24</v>
+      </c>
+      <c r="E321" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="F321" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="G321" t="n">
+        <v>340.53</v>
+      </c>
+      <c r="H321" t="n">
+        <v>330.49</v>
+      </c>
+      <c r="I321" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="J321" t="n">
+        <v>337</v>
+      </c>
+      <c r="K321" t="n">
+        <v>333.36</v>
+      </c>
+      <c r="L321" t="n">
+        <v>337.81</v>
+      </c>
+      <c r="M321" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="N321" t="n">
+        <v>335.36</v>
+      </c>
+      <c r="O321" t="n">
+        <v>332.85</v>
+      </c>
+      <c r="P321" t="n">
+        <v>343.75</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="R321" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="S321" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="T321" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="U321" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23500,7 +23572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26733,6 +26805,16 @@
       </c>
       <c r="B323" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -26901,28 +26983,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4087021029924899</v>
+        <v>-0.4055376656622033</v>
       </c>
       <c r="J2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K2" t="n">
         <v>319</v>
       </c>
-      <c r="K2" t="n">
-        <v>318</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2785748946176739</v>
+        <v>0.2761044169115255</v>
       </c>
       <c r="M2" t="n">
-        <v>3.66616514454332</v>
+        <v>3.671154193402561</v>
       </c>
       <c r="N2" t="n">
-        <v>23.89486890104848</v>
+        <v>23.90270288837938</v>
       </c>
       <c r="O2" t="n">
-        <v>4.888237811425348</v>
+        <v>4.889039055722441</v>
       </c>
       <c r="P2" t="n">
-        <v>372.6379738599701</v>
+        <v>372.6048691604311</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26979,28 +27061,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3521598525542254</v>
+        <v>-0.3478467211731892</v>
       </c>
       <c r="J3" t="n">
+        <v>320</v>
+      </c>
+      <c r="K3" t="n">
         <v>319</v>
       </c>
-      <c r="K3" t="n">
-        <v>318</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1761177358846479</v>
+        <v>0.1728395739395922</v>
       </c>
       <c r="M3" t="n">
-        <v>4.482700070684224</v>
+        <v>4.493132481398558</v>
       </c>
       <c r="N3" t="n">
-        <v>32.04670462973792</v>
+        <v>32.09995591432361</v>
       </c>
       <c r="O3" t="n">
-        <v>5.660980889363426</v>
+        <v>5.665682299098989</v>
       </c>
       <c r="P3" t="n">
-        <v>358.341985910249</v>
+        <v>358.2968641702559</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27057,28 +27139,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4161993869436146</v>
+        <v>-0.4123287808708201</v>
       </c>
       <c r="J4" t="n">
+        <v>320</v>
+      </c>
+      <c r="K4" t="n">
         <v>319</v>
       </c>
-      <c r="K4" t="n">
-        <v>318</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2269776299467762</v>
+        <v>0.2242167458606054</v>
       </c>
       <c r="M4" t="n">
-        <v>4.354583054569225</v>
+        <v>4.360500466170189</v>
       </c>
       <c r="N4" t="n">
-        <v>32.58768487458389</v>
+        <v>32.60931697022333</v>
       </c>
       <c r="O4" t="n">
-        <v>5.708562417507922</v>
+        <v>5.710456809242438</v>
       </c>
       <c r="P4" t="n">
-        <v>358.9172265465426</v>
+        <v>358.8767342764485</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27135,28 +27217,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4537958145412414</v>
+        <v>-0.4494567475996458</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2258718282281557</v>
+        <v>0.2229936791838153</v>
       </c>
       <c r="M5" t="n">
-        <v>4.914926402742555</v>
+        <v>4.921949582085428</v>
       </c>
       <c r="N5" t="n">
-        <v>38.97837463836142</v>
+        <v>39.01150333090941</v>
       </c>
       <c r="O5" t="n">
-        <v>6.243266343698739</v>
+        <v>6.245918934064819</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8373505350523</v>
+        <v>366.7918971624351</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27213,28 +27295,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3660876078243985</v>
+        <v>-0.3633662471156839</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1905457870310291</v>
+        <v>0.1889781975548077</v>
       </c>
       <c r="M6" t="n">
-        <v>4.459819191987655</v>
+        <v>4.458102908303132</v>
       </c>
       <c r="N6" t="n">
-        <v>31.44234591424918</v>
+        <v>31.40471612357991</v>
       </c>
       <c r="O6" t="n">
-        <v>5.607347493623807</v>
+        <v>5.60399108882053</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2002131579635</v>
+        <v>362.1717058719539</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27291,28 +27373,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3957141222148187</v>
+        <v>-0.3902937594011289</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1065095932813781</v>
+        <v>0.1042248528536019</v>
       </c>
       <c r="M7" t="n">
-        <v>6.470816841588502</v>
+        <v>6.484152789153166</v>
       </c>
       <c r="N7" t="n">
-        <v>72.35510447264319</v>
+        <v>72.37082016534482</v>
       </c>
       <c r="O7" t="n">
-        <v>8.506180369157663</v>
+        <v>8.507104099830025</v>
       </c>
       <c r="P7" t="n">
-        <v>342.1425648384544</v>
+        <v>342.0858021132799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27369,28 +27451,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4682343323042785</v>
+        <v>-0.4659087135164678</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2122583308056859</v>
+        <v>0.211546791754764</v>
       </c>
       <c r="M8" t="n">
-        <v>4.98162307394241</v>
+        <v>4.978285467860502</v>
       </c>
       <c r="N8" t="n">
-        <v>44.81779553415115</v>
+        <v>44.7222565494874</v>
       </c>
       <c r="O8" t="n">
-        <v>6.694609438507309</v>
+        <v>6.687470115782753</v>
       </c>
       <c r="P8" t="n">
-        <v>339.0620944569427</v>
+        <v>339.0377402827573</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27447,28 +27529,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4846561691678869</v>
+        <v>-0.4786465948759647</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L9" t="n">
-        <v>0.24922105104211</v>
+        <v>0.2444097151865879</v>
       </c>
       <c r="M9" t="n">
-        <v>4.762777149803229</v>
+        <v>4.775921690754187</v>
       </c>
       <c r="N9" t="n">
-        <v>38.97622397381933</v>
+        <v>39.15168062736103</v>
       </c>
       <c r="O9" t="n">
-        <v>6.243094102592026</v>
+        <v>6.257130382800172</v>
       </c>
       <c r="P9" t="n">
-        <v>341.9226640345972</v>
+        <v>341.8597310122751</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27525,28 +27607,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5495331941798439</v>
+        <v>-0.546065546577803</v>
       </c>
       <c r="J10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3200982505498129</v>
+        <v>0.3181919633631385</v>
       </c>
       <c r="M10" t="n">
-        <v>4.609878776603284</v>
+        <v>4.614286696950737</v>
       </c>
       <c r="N10" t="n">
-        <v>35.33097543352452</v>
+        <v>35.31953876331194</v>
       </c>
       <c r="O10" t="n">
-        <v>5.943986493383419</v>
+        <v>5.943024378488779</v>
       </c>
       <c r="P10" t="n">
-        <v>345.8603704371085</v>
+        <v>345.8240567926899</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27603,28 +27685,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6686141369124627</v>
+        <v>-0.6658181942671685</v>
       </c>
       <c r="J11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4641593380849579</v>
+        <v>0.4631757000142367</v>
       </c>
       <c r="M11" t="n">
-        <v>4.005880741797411</v>
+        <v>4.008004173947229</v>
       </c>
       <c r="N11" t="n">
-        <v>28.42657866118008</v>
+        <v>28.40208866219592</v>
       </c>
       <c r="O11" t="n">
-        <v>5.331658153068338</v>
+        <v>5.329360999425346</v>
       </c>
       <c r="P11" t="n">
-        <v>346.4646933217514</v>
+        <v>346.4354138566246</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27681,28 +27763,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6956569587121382</v>
+        <v>-0.6922974066557037</v>
       </c>
       <c r="J12" t="n">
+        <v>320</v>
+      </c>
+      <c r="K12" t="n">
         <v>319</v>
       </c>
-      <c r="K12" t="n">
-        <v>318</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.4611177176906078</v>
+        <v>0.4596377910419146</v>
       </c>
       <c r="M12" t="n">
-        <v>4.292962258028635</v>
+        <v>4.297410732487974</v>
       </c>
       <c r="N12" t="n">
-        <v>30.96004973777384</v>
+        <v>30.95514757742711</v>
       </c>
       <c r="O12" t="n">
-        <v>5.564175566764033</v>
+        <v>5.563735038391665</v>
       </c>
       <c r="P12" t="n">
-        <v>350.7387058730563</v>
+        <v>350.7033476709411</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27759,28 +27841,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7172803006185129</v>
+        <v>-0.7118902483400752</v>
       </c>
       <c r="J13" t="n">
+        <v>320</v>
+      </c>
+      <c r="K13" t="n">
         <v>319</v>
       </c>
-      <c r="K13" t="n">
-        <v>318</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.4422873674958245</v>
+        <v>0.4385764997026408</v>
       </c>
       <c r="M13" t="n">
-        <v>4.669852955645416</v>
+        <v>4.67941809823558</v>
       </c>
       <c r="N13" t="n">
-        <v>35.51509987157508</v>
+        <v>35.64097269145265</v>
       </c>
       <c r="O13" t="n">
-        <v>5.959454662263576</v>
+        <v>5.970006088058257</v>
       </c>
       <c r="P13" t="n">
-        <v>349.055108855293</v>
+        <v>348.9983802930706</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27837,28 +27919,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6846901673411186</v>
+        <v>-0.6776649029377266</v>
       </c>
       <c r="J14" t="n">
+        <v>320</v>
+      </c>
+      <c r="K14" t="n">
         <v>319</v>
       </c>
-      <c r="K14" t="n">
-        <v>318</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.4529479139772098</v>
+        <v>0.4462967387875156</v>
       </c>
       <c r="M14" t="n">
-        <v>4.294860091890786</v>
+        <v>4.31424205246331</v>
       </c>
       <c r="N14" t="n">
-        <v>30.99544555915205</v>
+        <v>31.30124306990072</v>
       </c>
       <c r="O14" t="n">
-        <v>5.567355346944548</v>
+        <v>5.59475138588845</v>
       </c>
       <c r="P14" t="n">
-        <v>342.0505607978147</v>
+        <v>341.9766221552469</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27915,28 +27997,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6529983859675905</v>
+        <v>-0.6448331209232603</v>
       </c>
       <c r="J15" t="n">
+        <v>320</v>
+      </c>
+      <c r="K15" t="n">
         <v>319</v>
       </c>
-      <c r="K15" t="n">
-        <v>318</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.4246189665934595</v>
+        <v>0.4159512165479656</v>
       </c>
       <c r="M15" t="n">
-        <v>4.448579665171581</v>
+        <v>4.480923566395836</v>
       </c>
       <c r="N15" t="n">
-        <v>31.63076207537637</v>
+        <v>32.07595733666498</v>
       </c>
       <c r="O15" t="n">
-        <v>5.624123227257416</v>
+        <v>5.663564013645911</v>
       </c>
       <c r="P15" t="n">
-        <v>336.8578864976253</v>
+        <v>336.7719497159019</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27993,28 +28075,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6336580659119218</v>
+        <v>-0.6238506941199498</v>
       </c>
       <c r="J16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L16" t="n">
-        <v>0.375185595541109</v>
+        <v>0.3645035915596819</v>
       </c>
       <c r="M16" t="n">
-        <v>4.858205188167409</v>
+        <v>4.894227449146527</v>
       </c>
       <c r="N16" t="n">
-        <v>36.83152659951168</v>
+        <v>37.50810952880715</v>
       </c>
       <c r="O16" t="n">
-        <v>6.068898301958246</v>
+        <v>6.124386461418577</v>
       </c>
       <c r="P16" t="n">
-        <v>344.4929742889011</v>
+        <v>344.3902702506575</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28071,28 +28153,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4220047551755315</v>
+        <v>-0.4134360398798368</v>
       </c>
       <c r="J17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2128732003756595</v>
+        <v>0.2044675666811371</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8660116170681</v>
+        <v>4.898476204720865</v>
       </c>
       <c r="N17" t="n">
-        <v>36.27131551306766</v>
+        <v>36.762301078745</v>
       </c>
       <c r="O17" t="n">
-        <v>6.022567186264315</v>
+        <v>6.063192317479712</v>
       </c>
       <c r="P17" t="n">
-        <v>343.6906716247066</v>
+        <v>343.600938954008</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28149,28 +28231,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4451733769800077</v>
+        <v>-0.4374897143816266</v>
       </c>
       <c r="J18" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K18" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2625428649064483</v>
+        <v>0.2541321083327075</v>
       </c>
       <c r="M18" t="n">
-        <v>4.486846696711054</v>
+        <v>4.51524534870766</v>
       </c>
       <c r="N18" t="n">
-        <v>30.6619547225969</v>
+        <v>31.05207512141176</v>
       </c>
       <c r="O18" t="n">
-        <v>5.537323787047034</v>
+        <v>5.572438884493194</v>
       </c>
       <c r="P18" t="n">
-        <v>341.7111094308701</v>
+        <v>341.6306451439955</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28227,28 +28309,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5121478258666962</v>
+        <v>-0.5052993869919018</v>
       </c>
       <c r="J19" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K19" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4066936863817341</v>
+        <v>0.3974533030722558</v>
       </c>
       <c r="M19" t="n">
-        <v>3.648159313049333</v>
+        <v>3.67374975065301</v>
       </c>
       <c r="N19" t="n">
-        <v>21.07691841457367</v>
+        <v>21.39708953414848</v>
       </c>
       <c r="O19" t="n">
-        <v>4.590960511110248</v>
+        <v>4.625698815762704</v>
       </c>
       <c r="P19" t="n">
-        <v>342.4740686767697</v>
+        <v>342.4023509584018</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28305,28 +28387,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3621712367854275</v>
+        <v>-0.3591451715744724</v>
       </c>
       <c r="J20" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K20" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2544027764558996</v>
+        <v>0.251821992970619</v>
       </c>
       <c r="M20" t="n">
-        <v>3.72081246565137</v>
+        <v>3.723377971693499</v>
       </c>
       <c r="N20" t="n">
-        <v>21.17460199158883</v>
+        <v>21.18380192269646</v>
       </c>
       <c r="O20" t="n">
-        <v>4.601586899276035</v>
+        <v>4.602586438373153</v>
       </c>
       <c r="P20" t="n">
-        <v>349.4514270447312</v>
+        <v>349.4197377069814</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28383,28 +28465,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1833927646987624</v>
+        <v>-0.1822055126044389</v>
       </c>
       <c r="J21" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K21" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06441907304587469</v>
+        <v>0.0640147251494404</v>
       </c>
       <c r="M21" t="n">
-        <v>3.88971902625606</v>
+        <v>3.885670611045249</v>
       </c>
       <c r="N21" t="n">
-        <v>26.90519795551004</v>
+        <v>26.8327211642839</v>
       </c>
       <c r="O21" t="n">
-        <v>5.187022070081256</v>
+        <v>5.180031000320741</v>
       </c>
       <c r="P21" t="n">
-        <v>350.4429758574515</v>
+        <v>350.4305428033074</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28442,7 +28524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V320"/>
+  <dimension ref="A1:V321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64241,6 +64323,118 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-41.31744679060778,175.86274100304595</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-41.317924061080426,175.86208672829332</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-41.31842002944007,175.8614706596668</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-41.318936138946626,175.86089978995176</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-41.31943373906868,175.86029819688352</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-41.31980918371314,175.8595253369746</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-41.320164391514645,175.85875813760617</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-41.32063970329164,175.8581249701071</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-41.321003807342244,175.8573788362314</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-41.321318837119065,175.856602632306</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-41.321624928334586,175.8558200301717</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-41.321884778387876,175.85499409045798</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-41.32210773382737,175.85414428692914</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-41.32233629282733,175.85331007149392</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-41.32260905503339,175.85248948370602</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-41.32288372308981,175.85166727026808</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>-41.323184895573135,175.85085588075876</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>-41.323529985469406,175.85008498365383</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>-41.32388686923661,175.84932360948682</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>-41.324281197617445,175.8485966019028</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V321"/>
+  <dimension ref="A1:V323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23556,6 +23556,150 @@
         <v>347.54</v>
       </c>
       <c r="V321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="C322" t="n">
+        <v>355</v>
+      </c>
+      <c r="D322" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="E322" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="F322" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="G322" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="H322" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="I322" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="J322" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="K322" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="L322" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="M322" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="N322" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="O322" t="n">
+        <v>330.57</v>
+      </c>
+      <c r="P322" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="R322" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="S322" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="T322" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="U322" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:01:01+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="C323" t="n">
+        <v>353.92</v>
+      </c>
+      <c r="D323" t="n">
+        <v>352.51</v>
+      </c>
+      <c r="E323" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="F323" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="G323" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="H323" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="I323" t="n">
+        <v>338.04</v>
+      </c>
+      <c r="J323" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="K323" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="L323" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="M323" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="N323" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="O323" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="P323" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>343.53</v>
+      </c>
+      <c r="R323" t="n">
+        <v>340.77</v>
+      </c>
+      <c r="S323" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="T323" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="U323" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="V323" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23572,7 +23716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26815,6 +26959,26 @@
       </c>
       <c r="B324" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -26983,28 +27147,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4055376656622033</v>
+        <v>-0.400027792468864</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2761044169115255</v>
+        <v>0.2722049255919657</v>
       </c>
       <c r="M2" t="n">
-        <v>3.671154193402561</v>
+        <v>3.676985852437848</v>
       </c>
       <c r="N2" t="n">
-        <v>23.90270288837938</v>
+        <v>23.88319825792836</v>
       </c>
       <c r="O2" t="n">
-        <v>4.889039055722441</v>
+        <v>4.887043918150149</v>
       </c>
       <c r="P2" t="n">
-        <v>372.6048691604311</v>
+        <v>372.5471459857638</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27061,28 +27225,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3478467211731892</v>
+        <v>-0.3413825920669001</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1728395739395922</v>
+        <v>0.1686114091694267</v>
       </c>
       <c r="M3" t="n">
-        <v>4.493132481398558</v>
+        <v>4.501559890196758</v>
       </c>
       <c r="N3" t="n">
-        <v>32.09995591432361</v>
+        <v>32.0773782852758</v>
       </c>
       <c r="O3" t="n">
-        <v>5.665682299098989</v>
+        <v>5.663689458760587</v>
       </c>
       <c r="P3" t="n">
-        <v>358.2968641702559</v>
+        <v>358.229143299769</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27139,28 +27303,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4123287808708201</v>
+        <v>-0.4060617306020979</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2242167458606054</v>
+        <v>0.2203104683744577</v>
       </c>
       <c r="M4" t="n">
-        <v>4.360500466170189</v>
+        <v>4.364936856723333</v>
       </c>
       <c r="N4" t="n">
-        <v>32.60931697022333</v>
+        <v>32.57389650056943</v>
       </c>
       <c r="O4" t="n">
-        <v>5.710456809242438</v>
+        <v>5.70735459740933</v>
       </c>
       <c r="P4" t="n">
-        <v>358.8767342764485</v>
+        <v>358.8110789254354</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27217,28 +27381,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4494567475996458</v>
+        <v>-0.4434877673500946</v>
       </c>
       <c r="J5" t="n">
+        <v>322</v>
+      </c>
+      <c r="K5" t="n">
         <v>320</v>
       </c>
-      <c r="K5" t="n">
-        <v>318</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2229936791838153</v>
+        <v>0.2199844905859581</v>
       </c>
       <c r="M5" t="n">
-        <v>4.921949582085428</v>
+        <v>4.921932056389231</v>
       </c>
       <c r="N5" t="n">
-        <v>39.01150333090941</v>
+        <v>38.91898279710004</v>
       </c>
       <c r="O5" t="n">
-        <v>6.245918934064819</v>
+        <v>6.238508058590615</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7918971624351</v>
+        <v>366.7292802201416</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27295,28 +27459,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3633662471156839</v>
+        <v>-0.3585283923231134</v>
       </c>
       <c r="J6" t="n">
+        <v>322</v>
+      </c>
+      <c r="K6" t="n">
         <v>320</v>
       </c>
-      <c r="K6" t="n">
-        <v>318</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1889781975548077</v>
+        <v>0.1864184688469404</v>
       </c>
       <c r="M6" t="n">
-        <v>4.458102908303132</v>
+        <v>4.451912373628189</v>
       </c>
       <c r="N6" t="n">
-        <v>31.40471612357991</v>
+        <v>31.30734704662344</v>
       </c>
       <c r="O6" t="n">
-        <v>5.60399108882053</v>
+        <v>5.595296868497992</v>
       </c>
       <c r="P6" t="n">
-        <v>362.1717058719539</v>
+        <v>362.1209541482039</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27373,28 +27537,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3902937594011289</v>
+        <v>-0.379889863428228</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1042248528536019</v>
+        <v>0.09990817836529253</v>
       </c>
       <c r="M7" t="n">
-        <v>6.484152789153166</v>
+        <v>6.508141037633253</v>
       </c>
       <c r="N7" t="n">
-        <v>72.37082016534482</v>
+        <v>72.37442468012095</v>
       </c>
       <c r="O7" t="n">
-        <v>8.507104099830025</v>
+        <v>8.507315950411208</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0858021132799</v>
+        <v>341.9766914026193</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27451,28 +27615,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4659087135164678</v>
+        <v>-0.4612397424899928</v>
       </c>
       <c r="J8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L8" t="n">
-        <v>0.211546791754764</v>
+        <v>0.2100513068652209</v>
       </c>
       <c r="M8" t="n">
-        <v>4.978285467860502</v>
+        <v>4.97168110753798</v>
       </c>
       <c r="N8" t="n">
-        <v>44.7222565494874</v>
+        <v>44.53596606869645</v>
       </c>
       <c r="O8" t="n">
-        <v>6.687470115782753</v>
+        <v>6.67352725840664</v>
       </c>
       <c r="P8" t="n">
-        <v>339.0377402827573</v>
+        <v>338.9887731099232</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27529,28 +27693,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4786465948759647</v>
+        <v>-0.4677578097579784</v>
       </c>
       <c r="J9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2444097151865879</v>
+        <v>0.2361061594010452</v>
       </c>
       <c r="M9" t="n">
-        <v>4.775921690754187</v>
+        <v>4.797270055254383</v>
       </c>
       <c r="N9" t="n">
-        <v>39.15168062736103</v>
+        <v>39.40503561335652</v>
       </c>
       <c r="O9" t="n">
-        <v>6.257130382800172</v>
+        <v>6.277343037731531</v>
       </c>
       <c r="P9" t="n">
-        <v>341.8597310122751</v>
+        <v>341.7455358252399</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27607,28 +27771,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.546065546577803</v>
+        <v>-0.5405141665009583</v>
       </c>
       <c r="J10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3181919633631385</v>
+        <v>0.3158304355771832</v>
       </c>
       <c r="M10" t="n">
-        <v>4.614286696950737</v>
+        <v>4.616130796480463</v>
       </c>
       <c r="N10" t="n">
-        <v>35.31953876331194</v>
+        <v>35.22961293125716</v>
       </c>
       <c r="O10" t="n">
-        <v>5.943024378488779</v>
+        <v>5.93545389429125</v>
       </c>
       <c r="P10" t="n">
-        <v>345.8240567926899</v>
+        <v>345.7658382562141</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27685,28 +27849,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6658181942671685</v>
+        <v>-0.6607072625568362</v>
       </c>
       <c r="J11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4631757000142367</v>
+        <v>0.4616673299694525</v>
       </c>
       <c r="M11" t="n">
-        <v>4.008004173947229</v>
+        <v>4.009903634628958</v>
       </c>
       <c r="N11" t="n">
-        <v>28.40208866219592</v>
+        <v>28.3350311123118</v>
       </c>
       <c r="O11" t="n">
-        <v>5.329360999425346</v>
+        <v>5.323065950400371</v>
       </c>
       <c r="P11" t="n">
-        <v>346.4354138566246</v>
+        <v>346.3818130913447</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27763,28 +27927,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6922974066557037</v>
+        <v>-0.6863606338102203</v>
       </c>
       <c r="J12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K12" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4596377910419146</v>
+        <v>0.457468663735531</v>
       </c>
       <c r="M12" t="n">
-        <v>4.297410732487974</v>
+        <v>4.302143808178092</v>
       </c>
       <c r="N12" t="n">
-        <v>30.95514757742711</v>
+        <v>30.90866021198925</v>
       </c>
       <c r="O12" t="n">
-        <v>5.563735038391665</v>
+        <v>5.559555756711974</v>
       </c>
       <c r="P12" t="n">
-        <v>350.7033476709411</v>
+        <v>350.6407731038058</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27841,28 +28005,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7118902483400752</v>
+        <v>-0.7033986932034048</v>
       </c>
       <c r="J13" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K13" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4385764997026408</v>
+        <v>0.4338545128053951</v>
       </c>
       <c r="M13" t="n">
-        <v>4.67941809823558</v>
+        <v>4.689676848158338</v>
       </c>
       <c r="N13" t="n">
-        <v>35.64097269145265</v>
+        <v>35.7189772150614</v>
       </c>
       <c r="O13" t="n">
-        <v>5.970006088058257</v>
+        <v>5.976535552898635</v>
       </c>
       <c r="P13" t="n">
-        <v>348.9983802930706</v>
+        <v>348.9088805619911</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27919,28 +28083,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6776649029377266</v>
+        <v>-0.6673961726878631</v>
       </c>
       <c r="J14" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K14" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4462967387875156</v>
+        <v>0.4385426261030309</v>
       </c>
       <c r="M14" t="n">
-        <v>4.31424205246331</v>
+        <v>4.335033848925568</v>
       </c>
       <c r="N14" t="n">
-        <v>31.30124306990072</v>
+        <v>31.54891081656538</v>
       </c>
       <c r="O14" t="n">
-        <v>5.59475138588845</v>
+        <v>5.616841711902284</v>
       </c>
       <c r="P14" t="n">
-        <v>341.9766221552469</v>
+        <v>341.8683943618225</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27997,28 +28161,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6448331209232603</v>
+        <v>-0.6328386855155409</v>
       </c>
       <c r="J15" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K15" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4159512165479656</v>
+        <v>0.4055288231587169</v>
       </c>
       <c r="M15" t="n">
-        <v>4.480923566395836</v>
+        <v>4.522428861607321</v>
       </c>
       <c r="N15" t="n">
-        <v>32.07595733666498</v>
+        <v>32.47933169940387</v>
       </c>
       <c r="O15" t="n">
-        <v>5.663564013645911</v>
+        <v>5.699064107325331</v>
       </c>
       <c r="P15" t="n">
-        <v>336.7719497159019</v>
+        <v>336.6455333794675</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28075,28 +28239,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6238506941199498</v>
+        <v>-0.6085449604126308</v>
       </c>
       <c r="J16" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K16" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3645035915596819</v>
+        <v>0.350141167966033</v>
       </c>
       <c r="M16" t="n">
-        <v>4.894227449146527</v>
+        <v>4.945518371479532</v>
       </c>
       <c r="N16" t="n">
-        <v>37.50810952880715</v>
+        <v>38.26001433515082</v>
       </c>
       <c r="O16" t="n">
-        <v>6.124386461418577</v>
+        <v>6.185467996453528</v>
       </c>
       <c r="P16" t="n">
-        <v>344.3902702506575</v>
+        <v>344.229756219218</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28153,28 +28317,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4134360398798368</v>
+        <v>-0.3995106589698024</v>
       </c>
       <c r="J17" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K17" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2044675666811371</v>
+        <v>0.1921701794463503</v>
       </c>
       <c r="M17" t="n">
-        <v>4.898476204720865</v>
+        <v>4.946447438088595</v>
       </c>
       <c r="N17" t="n">
-        <v>36.762301078745</v>
+        <v>37.34862047594043</v>
       </c>
       <c r="O17" t="n">
-        <v>6.063192317479712</v>
+        <v>6.111351771575617</v>
       </c>
       <c r="P17" t="n">
-        <v>343.600938954008</v>
+        <v>343.4549005233781</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28231,28 +28395,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4374897143816266</v>
+        <v>-0.4242507554170563</v>
       </c>
       <c r="J18" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K18" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2541321083327075</v>
+        <v>0.2407720666208851</v>
       </c>
       <c r="M18" t="n">
-        <v>4.51524534870766</v>
+        <v>4.561923590774648</v>
       </c>
       <c r="N18" t="n">
-        <v>31.05207512141176</v>
+        <v>31.59331987947139</v>
       </c>
       <c r="O18" t="n">
-        <v>5.572438884493194</v>
+        <v>5.620793527560979</v>
       </c>
       <c r="P18" t="n">
-        <v>341.6306451439955</v>
+        <v>341.4918029419353</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28309,28 +28473,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5052993869919018</v>
+        <v>-0.4931724520215698</v>
       </c>
       <c r="J19" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K19" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3974533030722558</v>
+        <v>0.3822490430556557</v>
       </c>
       <c r="M19" t="n">
-        <v>3.67374975065301</v>
+        <v>3.717577092484521</v>
       </c>
       <c r="N19" t="n">
-        <v>21.39708953414848</v>
+        <v>21.88006346156124</v>
       </c>
       <c r="O19" t="n">
-        <v>4.625698815762704</v>
+        <v>4.67761300895673</v>
       </c>
       <c r="P19" t="n">
-        <v>342.4023509584018</v>
+        <v>342.275170786433</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28387,28 +28551,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3591451715744724</v>
+        <v>-0.354249273502557</v>
       </c>
       <c r="J20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L20" t="n">
-        <v>0.251821992970619</v>
+        <v>0.248259683383897</v>
       </c>
       <c r="M20" t="n">
-        <v>3.723377971693499</v>
+        <v>3.723234592430861</v>
       </c>
       <c r="N20" t="n">
-        <v>21.18380192269646</v>
+        <v>21.15258847575671</v>
       </c>
       <c r="O20" t="n">
-        <v>4.602586438373153</v>
+        <v>4.599194328983796</v>
       </c>
       <c r="P20" t="n">
-        <v>349.4197377069814</v>
+        <v>349.368392277511</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28465,28 +28629,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1822055126044389</v>
+        <v>-0.180536127012994</v>
       </c>
       <c r="J21" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K21" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0640147251494404</v>
+        <v>0.06367760625332641</v>
       </c>
       <c r="M21" t="n">
-        <v>3.885670611045249</v>
+        <v>3.87287833968505</v>
       </c>
       <c r="N21" t="n">
-        <v>26.8327211642839</v>
+        <v>26.67785221905828</v>
       </c>
       <c r="O21" t="n">
-        <v>5.180031000320741</v>
+        <v>5.165060717848173</v>
       </c>
       <c r="P21" t="n">
-        <v>350.4305428033074</v>
+        <v>350.4130359874299</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28524,7 +28688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V321"/>
+  <dimension ref="A1:V323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64435,6 +64599,230 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-41.31744673724537,175.86274090689378</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-41.31791802442339,175.86207662087355</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-41.31841754389317,175.86146704109785</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-41.3189268048818,175.86088539864548</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-41.31943309747749,175.86029719652777</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-41.31980866101684,175.85952467994755</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-41.320163703586594,175.85875736756782</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-41.320636073147675,175.85812124259277</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-41.32099821473315,175.85737382022768</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-41.321316865989715,175.85660119215635</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-41.32162008582069,175.85581713765058</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-41.32187360914671,175.85498774034892</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-41.32209151769245,175.8541350676164</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-41.32231700782381,175.85330075841551</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-41.32258918153489,175.85247987156447</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-41.32287065270579,175.85165842709543</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>-41.32317591906509,175.8508483484605</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>-41.32352371071936,175.85007982737176</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>-41.32388101599248,175.84931868525655</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>-41.324278251883854,175.84859385535705</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:01:01+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-41.317440920741895,175.8627304263054</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-41.31791198776541,175.86206651345566</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-41.31840954164375,175.8614553910729</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-41.31892116921908,175.86087670955686</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-41.31942983119496,175.86029210380792</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-41.319807876972405,175.859523694407</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-41.32016638650597,175.85876037071748</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-41.32063343951373,175.8581185383179</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-41.32099418805444,175.85737020870553</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-41.32131615638317,175.8566006737025</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-41.32162115281529,175.85581777498572</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-41.32186823136377,175.85498468288975</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-41.32207695626439,175.8541267890539</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-41.32230068323675,175.8532928749808</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-41.322575312369345,175.85247316352036</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-41.32285974735407,175.85165104874557</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>-41.32317188724351,175.85084496531027</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>-41.32352049682289,175.85007718634958</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>-41.32387995176624,175.84931778994203</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>-41.32427611622697,175.84859186411148</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V323"/>
+  <dimension ref="A1:V326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23700,6 +23700,222 @@
         <v>346.85</v>
       </c>
       <c r="V323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="C324" t="n">
+        <v>352.96</v>
+      </c>
+      <c r="D324" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="E324" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="F324" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="G324" t="n">
+        <v>339.48</v>
+      </c>
+      <c r="H324" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="I324" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="J324" t="n">
+        <v>335.23</v>
+      </c>
+      <c r="K324" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="L324" t="n">
+        <v>338.12</v>
+      </c>
+      <c r="M324" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="N324" t="n">
+        <v>331.46</v>
+      </c>
+      <c r="O324" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="P324" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="R324" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="S324" t="n">
+        <v>339.35</v>
+      </c>
+      <c r="T324" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="U324" t="n">
+        <v>348.03</v>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="C325" t="n">
+        <v>350.93</v>
+      </c>
+      <c r="D325" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="E325" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="F325" t="n">
+        <v>355.57</v>
+      </c>
+      <c r="G325" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="H325" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="I325" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="J325" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="K325" t="n">
+        <v>333.53</v>
+      </c>
+      <c r="L325" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="M325" t="n">
+        <v>338.09</v>
+      </c>
+      <c r="N325" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="O325" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="P325" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="R325" t="n">
+        <v>340.99</v>
+      </c>
+      <c r="S325" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="T325" t="n">
+        <v>344.96</v>
+      </c>
+      <c r="U325" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>363.41</v>
+      </c>
+      <c r="C326" t="n">
+        <v>348.05</v>
+      </c>
+      <c r="D326" t="n">
+        <v>348.68</v>
+      </c>
+      <c r="E326" t="n">
+        <v>353.49</v>
+      </c>
+      <c r="F326" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="G326" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="H326" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="I326" t="n">
+        <v>333.9</v>
+      </c>
+      <c r="J326" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="K326" t="n">
+        <v>335.04</v>
+      </c>
+      <c r="L326" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="M326" t="n">
+        <v>337.73</v>
+      </c>
+      <c r="N326" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="O326" t="n">
+        <v>324.93</v>
+      </c>
+      <c r="P326" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="R326" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="S326" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="T326" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="U326" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="V326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23716,7 +23932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B326"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26979,6 +27195,36 @@
       </c>
       <c r="B326" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -27147,28 +27393,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.400027792468864</v>
+        <v>-0.3955338555247798</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2722049255919657</v>
+        <v>0.2710980242128135</v>
       </c>
       <c r="M2" t="n">
-        <v>3.676985852437848</v>
+        <v>3.666079012924283</v>
       </c>
       <c r="N2" t="n">
-        <v>23.88319825792836</v>
+        <v>23.72616787517802</v>
       </c>
       <c r="O2" t="n">
-        <v>4.887043918150149</v>
+        <v>4.870951434286531</v>
       </c>
       <c r="P2" t="n">
-        <v>372.5471459857638</v>
+        <v>372.4997653507011</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27225,28 +27471,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3413825920669001</v>
+        <v>-0.3387217792281765</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1686114091694267</v>
+        <v>0.1689275262197757</v>
       </c>
       <c r="M3" t="n">
-        <v>4.501559890196758</v>
+        <v>4.481533490041819</v>
       </c>
       <c r="N3" t="n">
-        <v>32.0773782852758</v>
+        <v>31.83773901348134</v>
       </c>
       <c r="O3" t="n">
-        <v>5.663689458760587</v>
+        <v>5.642494041953553</v>
       </c>
       <c r="P3" t="n">
-        <v>358.229143299769</v>
+        <v>358.2011247929668</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27303,28 +27549,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4060617306020979</v>
+        <v>-0.4020680582920824</v>
       </c>
       <c r="J4" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2203104683744577</v>
+        <v>0.2199878839211852</v>
       </c>
       <c r="M4" t="n">
-        <v>4.364936856723333</v>
+        <v>4.344637225553433</v>
       </c>
       <c r="N4" t="n">
-        <v>32.57389650056943</v>
+        <v>32.33100690149095</v>
       </c>
       <c r="O4" t="n">
-        <v>5.70735459740933</v>
+        <v>5.686036132622704</v>
       </c>
       <c r="P4" t="n">
-        <v>358.8110789254354</v>
+        <v>358.7689835026819</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27381,28 +27627,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4434877673500946</v>
+        <v>-0.4413675512720916</v>
       </c>
       <c r="J5" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2199844905859581</v>
+        <v>0.2214933125069971</v>
       </c>
       <c r="M5" t="n">
-        <v>4.921932056389231</v>
+        <v>4.896097317057533</v>
       </c>
       <c r="N5" t="n">
-        <v>38.91898279710004</v>
+        <v>38.60879746894073</v>
       </c>
       <c r="O5" t="n">
-        <v>6.238508058590615</v>
+        <v>6.213597787831196</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7292802201416</v>
+        <v>366.7069344167039</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27459,28 +27705,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3585283923231134</v>
+        <v>-0.3529253115198649</v>
       </c>
       <c r="J6" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1864184688469404</v>
+        <v>0.18420077669746</v>
       </c>
       <c r="M6" t="n">
-        <v>4.451912373628189</v>
+        <v>4.43543056145708</v>
       </c>
       <c r="N6" t="n">
-        <v>31.30734704662344</v>
+        <v>31.10578651322278</v>
       </c>
       <c r="O6" t="n">
-        <v>5.595296868497992</v>
+        <v>5.577256181423154</v>
       </c>
       <c r="P6" t="n">
-        <v>362.1209541482039</v>
+        <v>362.0617766041674</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27537,28 +27783,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.379889863428228</v>
+        <v>-0.3684176953733909</v>
       </c>
       <c r="J7" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09990817836529253</v>
+        <v>0.09576509903264774</v>
       </c>
       <c r="M7" t="n">
-        <v>6.508141037633253</v>
+        <v>6.517838948399241</v>
       </c>
       <c r="N7" t="n">
-        <v>72.37442468012095</v>
+        <v>72.09063631565428</v>
       </c>
       <c r="O7" t="n">
-        <v>8.507315950411208</v>
+        <v>8.490620490615175</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9766914026193</v>
+        <v>341.8555970828119</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27615,28 +27861,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4612397424899928</v>
+        <v>-0.4554735177584617</v>
       </c>
       <c r="J8" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K8" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2100513068652209</v>
+        <v>0.208789892504241</v>
       </c>
       <c r="M8" t="n">
-        <v>4.97168110753798</v>
+        <v>4.955096479874173</v>
       </c>
       <c r="N8" t="n">
-        <v>44.53596606869645</v>
+        <v>44.22140233989762</v>
       </c>
       <c r="O8" t="n">
-        <v>6.67352725840664</v>
+        <v>6.649917468653097</v>
       </c>
       <c r="P8" t="n">
-        <v>338.9887731099232</v>
+        <v>338.9279061575609</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27693,28 +27939,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4677578097579784</v>
+        <v>-0.4566891678887952</v>
       </c>
       <c r="J9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2361061594010452</v>
+        <v>0.2294411966945172</v>
       </c>
       <c r="M9" t="n">
-        <v>4.797270055254383</v>
+        <v>4.804830080507036</v>
       </c>
       <c r="N9" t="n">
-        <v>39.40503561335652</v>
+        <v>39.40031566349028</v>
       </c>
       <c r="O9" t="n">
-        <v>6.277343037731531</v>
+        <v>6.276967075227516</v>
       </c>
       <c r="P9" t="n">
-        <v>341.7455358252399</v>
+        <v>341.6287023565852</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27771,28 +28017,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5405141665009583</v>
+        <v>-0.5352472541062757</v>
       </c>
       <c r="J10" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K10" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3158304355771832</v>
+        <v>0.3153116079823824</v>
       </c>
       <c r="M10" t="n">
-        <v>4.616130796480463</v>
+        <v>4.6019236292089</v>
       </c>
       <c r="N10" t="n">
-        <v>35.22961293125716</v>
+        <v>34.99337204060102</v>
       </c>
       <c r="O10" t="n">
-        <v>5.93545389429125</v>
+        <v>5.915519591768843</v>
       </c>
       <c r="P10" t="n">
-        <v>345.7658382562141</v>
+        <v>345.710255159212</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27849,28 +28095,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6607072625568362</v>
+        <v>-0.651553164784898</v>
       </c>
       <c r="J11" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K11" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4616673299694525</v>
+        <v>0.4575016422844306</v>
       </c>
       <c r="M11" t="n">
-        <v>4.009903634628958</v>
+        <v>4.020561359933589</v>
       </c>
       <c r="N11" t="n">
-        <v>28.3350311123118</v>
+        <v>28.31583546156362</v>
       </c>
       <c r="O11" t="n">
-        <v>5.323065950400371</v>
+        <v>5.321262581527397</v>
       </c>
       <c r="P11" t="n">
-        <v>346.3818130913447</v>
+        <v>346.2851474227222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27927,28 +28173,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6863606338102203</v>
+        <v>-0.6740867826399261</v>
       </c>
       <c r="J12" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K12" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L12" t="n">
-        <v>0.457468663735531</v>
+        <v>0.4499502114367718</v>
       </c>
       <c r="M12" t="n">
-        <v>4.302143808178092</v>
+        <v>4.326414304084904</v>
       </c>
       <c r="N12" t="n">
-        <v>30.90866021198925</v>
+        <v>31.0545288539543</v>
       </c>
       <c r="O12" t="n">
-        <v>5.559555756711974</v>
+        <v>5.572659046985945</v>
       </c>
       <c r="P12" t="n">
-        <v>350.6407731038058</v>
+        <v>350.5105168124539</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28005,28 +28251,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7033986932034048</v>
+        <v>-0.6899536103456857</v>
       </c>
       <c r="J13" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K13" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4338545128053951</v>
+        <v>0.4257507846396209</v>
       </c>
       <c r="M13" t="n">
-        <v>4.689676848158338</v>
+        <v>4.708849955872025</v>
       </c>
       <c r="N13" t="n">
-        <v>35.7189772150614</v>
+        <v>35.89554206235748</v>
       </c>
       <c r="O13" t="n">
-        <v>5.976535552898635</v>
+        <v>5.991288848182625</v>
       </c>
       <c r="P13" t="n">
-        <v>348.9088805619911</v>
+        <v>348.7662183504579</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28083,28 +28329,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6673961726878631</v>
+        <v>-0.6555881336049917</v>
       </c>
       <c r="J14" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K14" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4385426261030309</v>
+        <v>0.4314964609770428</v>
       </c>
       <c r="M14" t="n">
-        <v>4.335033848925568</v>
+        <v>4.348594070795624</v>
       </c>
       <c r="N14" t="n">
-        <v>31.54891081656538</v>
+        <v>31.65730075367773</v>
       </c>
       <c r="O14" t="n">
-        <v>5.616841711902284</v>
+        <v>5.626482093962242</v>
       </c>
       <c r="P14" t="n">
-        <v>341.8683943618225</v>
+        <v>341.7431280931287</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28161,28 +28407,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6328386855155409</v>
+        <v>-0.6200130406713285</v>
       </c>
       <c r="J15" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K15" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4055288231587169</v>
+        <v>0.3968640845365135</v>
       </c>
       <c r="M15" t="n">
-        <v>4.522428861607321</v>
+        <v>4.553276745572429</v>
       </c>
       <c r="N15" t="n">
-        <v>32.47933169940387</v>
+        <v>32.66110098061243</v>
       </c>
       <c r="O15" t="n">
-        <v>5.699064107325331</v>
+        <v>5.71498914964958</v>
       </c>
       <c r="P15" t="n">
-        <v>336.6455333794675</v>
+        <v>336.5094826178474</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28239,28 +28485,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6085449604126308</v>
+        <v>-0.5907964015731832</v>
       </c>
       <c r="J16" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K16" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L16" t="n">
-        <v>0.350141167966033</v>
+        <v>0.3359495740856483</v>
       </c>
       <c r="M16" t="n">
-        <v>4.945518371479532</v>
+        <v>4.996318479071848</v>
       </c>
       <c r="N16" t="n">
-        <v>38.26001433515082</v>
+        <v>38.80847167563333</v>
       </c>
       <c r="O16" t="n">
-        <v>6.185467996453528</v>
+        <v>6.229644586622364</v>
       </c>
       <c r="P16" t="n">
-        <v>344.229756219218</v>
+        <v>344.0423961304575</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28317,28 +28563,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3995106589698024</v>
+        <v>-0.3817000646721397</v>
       </c>
       <c r="J17" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K17" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1921701794463503</v>
+        <v>0.1777702420084477</v>
       </c>
       <c r="M17" t="n">
-        <v>4.946447438088595</v>
+        <v>5.000255544070302</v>
       </c>
       <c r="N17" t="n">
-        <v>37.34862047594043</v>
+        <v>37.90552241255494</v>
       </c>
       <c r="O17" t="n">
-        <v>6.111351771575617</v>
+        <v>6.156746089660913</v>
       </c>
       <c r="P17" t="n">
-        <v>343.4549005233781</v>
+        <v>343.2668762429343</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28395,28 +28641,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4242507554170563</v>
+        <v>-0.406178720225021</v>
       </c>
       <c r="J18" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K18" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2407720666208851</v>
+        <v>0.2235682393793541</v>
       </c>
       <c r="M18" t="n">
-        <v>4.561923590774648</v>
+        <v>4.623203915837221</v>
       </c>
       <c r="N18" t="n">
-        <v>31.59331987947139</v>
+        <v>32.22933998005598</v>
       </c>
       <c r="O18" t="n">
-        <v>5.620793527560979</v>
+        <v>5.677089041054049</v>
       </c>
       <c r="P18" t="n">
-        <v>341.4918029419353</v>
+        <v>341.3010172919705</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28473,28 +28719,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4931724520215698</v>
+        <v>-0.4748792083829218</v>
       </c>
       <c r="J19" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K19" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3822490430556557</v>
+        <v>0.3592675843876575</v>
       </c>
       <c r="M19" t="n">
-        <v>3.717577092484521</v>
+        <v>3.788640697986245</v>
       </c>
       <c r="N19" t="n">
-        <v>21.88006346156124</v>
+        <v>22.62293070447069</v>
       </c>
       <c r="O19" t="n">
-        <v>4.67761300895673</v>
+        <v>4.756356873119456</v>
       </c>
       <c r="P19" t="n">
-        <v>342.275170786433</v>
+        <v>342.0820328890556</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28551,28 +28797,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.354249273502557</v>
+        <v>-0.3457133464258273</v>
       </c>
       <c r="J20" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K20" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L20" t="n">
-        <v>0.248259683383897</v>
+        <v>0.2410822119682667</v>
       </c>
       <c r="M20" t="n">
-        <v>3.723234592430861</v>
+        <v>3.729098877163096</v>
       </c>
       <c r="N20" t="n">
-        <v>21.15258847575671</v>
+        <v>21.16341504234908</v>
       </c>
       <c r="O20" t="n">
-        <v>4.599194328983796</v>
+        <v>4.60037118527941</v>
       </c>
       <c r="P20" t="n">
-        <v>349.368392277511</v>
+        <v>349.2782692482899</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28629,28 +28875,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.180536127012994</v>
+        <v>-0.174924516963861</v>
       </c>
       <c r="J21" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K21" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06367760625332641</v>
+        <v>0.06093749927486625</v>
       </c>
       <c r="M21" t="n">
-        <v>3.87287833968505</v>
+        <v>3.874712629431413</v>
       </c>
       <c r="N21" t="n">
-        <v>26.67785221905828</v>
+        <v>26.52376244152131</v>
       </c>
       <c r="O21" t="n">
-        <v>5.165060717848173</v>
+        <v>5.150122565679511</v>
       </c>
       <c r="P21" t="n">
-        <v>350.4130359874299</v>
+        <v>350.3537758597204</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28688,7 +28934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V323"/>
+  <dimension ref="A1:V326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64823,6 +65069,342 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-41.31743894633223,175.86272686867488</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-41.317906621846404,175.86205752908572</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-41.31840420681011,175.86144762439116</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-41.31891588578463,175.86086856353765</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-41.31942755646233,175.86028855709262</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-41.319802323324,175.85951671349545</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-41.32016363479378,175.858757290564</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-41.3206241862047,175.85810903681337</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-41.32099060878438,175.85736699846402</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-41.32131804866733,175.85660205624612</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-41.32162747270626,175.85582154997118</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-41.321871788974036,175.85498670551652</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-41.32207546702738,175.85412594238295</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-41.32230042948668,175.85329275244044</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-41.32256998458,175.85247058665055</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-41.32285814362582,175.85164996369434</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>-41.323171963315616,175.85084502914327</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>-41.323524093326064,175.85008014177916</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>-41.323884284687274,175.84932143515127</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>-41.32428480614097,175.84859996642174</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-41.31743270292791,175.86271561887176</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-41.31789527516102,175.86203853089165</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-41.318397174528535,175.86143738649446</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-41.31890390999758,175.86085009923224</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-41.31942563168848,175.86028555602604</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-41.31979748838265,175.85951063599697</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-41.32016308445134,175.85875667453334</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-41.320618278322335,175.8581029704696</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-41.320988744581165,175.85736532646337</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-41.321320177486996,175.8566036116078</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-41.32163420297958,175.85582557008638</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-41.321878490518834,175.85499051558148</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-41.32207521882123,175.85412580127115</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-41.32229002573392,175.85328772828476</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-41.32256431851825,175.85246784617044</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-41.322859105862776,175.8516506147251</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-41.323173560829844,175.8508463696367</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>-41.323525011582184,175.85008089635696</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>-41.32388793346278,175.84932450480153</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>-41.32429010846106,175.84860491020538</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-41.31742763349618,175.86270648441777</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-41.31787917739468,175.8620115777999</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-41.31838632298862,175.86142158836503</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-41.31888665076941,175.8608234889216</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-41.319426448259215,175.8602868292058</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-41.319784290297726,175.85949404607328</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-41.320155448449505,175.85874812710895</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-41.3206039712804,175.8580882796899</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-41.32097271243248,175.85735094726178</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-41.32133208310765,175.85661231011397</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-41.32164807390823,175.85583385544854</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-41.3218755120545,175.85498882221916</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-41.32205709977038,175.85411550011128</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-41.322269302810895,175.85327772082528</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-41.32254723576436,175.85245958383052</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-41.322845073240195,175.85164112052885</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>-41.32316055249917,175.85083545419212</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>-41.32352485853951,175.85008077059402</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>-41.323886489155825,175.8493232897316</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>-41.32429555806757,175.84860999131718</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V326"/>
+  <dimension ref="A1:V327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23918,6 +23918,78 @@
       <c r="V326" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="C327" t="n">
+        <v>347.99</v>
+      </c>
+      <c r="D327" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="E327" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="F327" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="G327" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="H327" t="n">
+        <v>329.61</v>
+      </c>
+      <c r="I327" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="J327" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="K327" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="L327" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="M327" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="N327" t="n">
+        <v>328.41</v>
+      </c>
+      <c r="O327" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="P327" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>340.65</v>
+      </c>
+      <c r="R327" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="S327" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="T327" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="U327" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23932,7 +24004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27225,6 +27297,16 @@
       </c>
       <c r="B329" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -27393,28 +27475,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3955338555247798</v>
+        <v>-0.3947133547203725</v>
       </c>
       <c r="J2" t="n">
+        <v>326</v>
+      </c>
+      <c r="K2" t="n">
         <v>325</v>
       </c>
-      <c r="K2" t="n">
-        <v>324</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2710980242128135</v>
+        <v>0.2715182386793363</v>
       </c>
       <c r="M2" t="n">
-        <v>3.666079012924283</v>
+        <v>3.658967352456566</v>
       </c>
       <c r="N2" t="n">
-        <v>23.72616787517802</v>
+        <v>23.65898520095136</v>
       </c>
       <c r="O2" t="n">
-        <v>4.870951434286531</v>
+        <v>4.864050287666787</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4997653507011</v>
+        <v>372.4910712994616</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27471,28 +27553,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3387217792281765</v>
+        <v>-0.3394148554963347</v>
       </c>
       <c r="J3" t="n">
+        <v>326</v>
+      </c>
+      <c r="K3" t="n">
         <v>325</v>
       </c>
-      <c r="K3" t="n">
-        <v>324</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1689275262197757</v>
+        <v>0.1704042148801257</v>
       </c>
       <c r="M3" t="n">
-        <v>4.481533490041819</v>
+        <v>4.471020327486012</v>
       </c>
       <c r="N3" t="n">
-        <v>31.83773901348134</v>
+        <v>31.74393006164398</v>
       </c>
       <c r="O3" t="n">
-        <v>5.642494041953553</v>
+        <v>5.634175189115438</v>
       </c>
       <c r="P3" t="n">
-        <v>358.2011247929668</v>
+        <v>358.2084686499819</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27549,28 +27631,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4020680582920824</v>
+        <v>-0.4017713402277486</v>
       </c>
       <c r="J4" t="n">
+        <v>326</v>
+      </c>
+      <c r="K4" t="n">
         <v>325</v>
       </c>
-      <c r="K4" t="n">
-        <v>324</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2199878839211852</v>
+        <v>0.2208512832196421</v>
       </c>
       <c r="M4" t="n">
-        <v>4.344637225553433</v>
+        <v>4.332760274993841</v>
       </c>
       <c r="N4" t="n">
-        <v>32.33100690149095</v>
+        <v>32.23228812012407</v>
       </c>
       <c r="O4" t="n">
-        <v>5.686036132622704</v>
+        <v>5.677348687558663</v>
       </c>
       <c r="P4" t="n">
-        <v>358.7689835026819</v>
+        <v>358.7658394691342</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27627,28 +27709,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4413675512720916</v>
+        <v>-0.4427042427961592</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2214933125069971</v>
+        <v>0.2235979261704557</v>
       </c>
       <c r="M5" t="n">
-        <v>4.896097317057533</v>
+        <v>4.887896264462946</v>
       </c>
       <c r="N5" t="n">
-        <v>38.60879746894073</v>
+        <v>38.50509472009965</v>
       </c>
       <c r="O5" t="n">
-        <v>6.213597787831196</v>
+        <v>6.205247353659614</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7069344167039</v>
+        <v>366.721117374815</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27705,28 +27787,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3529253115198649</v>
+        <v>-0.3511570832770056</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L6" t="n">
-        <v>0.18420077669746</v>
+        <v>0.1835405306634276</v>
       </c>
       <c r="M6" t="n">
-        <v>4.43543056145708</v>
+        <v>4.429650724598465</v>
       </c>
       <c r="N6" t="n">
-        <v>31.10578651322278</v>
+        <v>31.03683487825739</v>
       </c>
       <c r="O6" t="n">
-        <v>5.577256181423154</v>
+        <v>5.57107125050985</v>
       </c>
       <c r="P6" t="n">
-        <v>362.0617766041674</v>
+        <v>362.0430148280598</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27783,28 +27865,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3684176953733909</v>
+        <v>-0.3667296955655689</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09576509903264774</v>
+        <v>0.09550611842853685</v>
       </c>
       <c r="M7" t="n">
-        <v>6.517838948399241</v>
+        <v>6.507989691851438</v>
       </c>
       <c r="N7" t="n">
-        <v>72.09063631565428</v>
+        <v>71.89404250458078</v>
       </c>
       <c r="O7" t="n">
-        <v>8.490620490615175</v>
+        <v>8.479035470180602</v>
       </c>
       <c r="P7" t="n">
-        <v>341.8555970828119</v>
+        <v>341.8376939558855</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27861,28 +27943,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4554735177584617</v>
+        <v>-0.453785048964173</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L8" t="n">
-        <v>0.208789892504241</v>
+        <v>0.2085499424655491</v>
       </c>
       <c r="M8" t="n">
-        <v>4.955096479874173</v>
+        <v>4.948355917467667</v>
       </c>
       <c r="N8" t="n">
-        <v>44.22140233989762</v>
+        <v>44.11031061639729</v>
       </c>
       <c r="O8" t="n">
-        <v>6.649917468653097</v>
+        <v>6.641559351266635</v>
       </c>
       <c r="P8" t="n">
-        <v>338.9279061575609</v>
+        <v>338.9099980565082</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27939,28 +28021,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4566891678887952</v>
+        <v>-0.4538750143996267</v>
       </c>
       <c r="J9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2294411966945172</v>
+        <v>0.2281063191060153</v>
       </c>
       <c r="M9" t="n">
-        <v>4.804830080507036</v>
+        <v>4.803375457713761</v>
       </c>
       <c r="N9" t="n">
-        <v>39.40031566349028</v>
+        <v>39.34767087631887</v>
       </c>
       <c r="O9" t="n">
-        <v>6.276967075227516</v>
+        <v>6.27277218431523</v>
       </c>
       <c r="P9" t="n">
-        <v>341.6287023565852</v>
+        <v>341.5988551096402</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28017,28 +28099,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5352472541062757</v>
+        <v>-0.5352832800371294</v>
       </c>
       <c r="J10" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K10" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3153116079823824</v>
+        <v>0.3167524858262043</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6019236292089</v>
+        <v>4.587982351272403</v>
       </c>
       <c r="N10" t="n">
-        <v>34.99337204060102</v>
+        <v>34.88604158789069</v>
       </c>
       <c r="O10" t="n">
-        <v>5.915519591768843</v>
+        <v>5.906440686901942</v>
       </c>
       <c r="P10" t="n">
-        <v>345.710255159212</v>
+        <v>345.7106372545236</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28095,28 +28177,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.651553164784898</v>
+        <v>-0.6490975307561974</v>
       </c>
       <c r="J11" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4575016422844306</v>
+        <v>0.4567922197750252</v>
       </c>
       <c r="M11" t="n">
-        <v>4.020561359933589</v>
+        <v>4.021142524578003</v>
       </c>
       <c r="N11" t="n">
-        <v>28.31583546156362</v>
+        <v>28.28091828464109</v>
       </c>
       <c r="O11" t="n">
-        <v>5.321262581527397</v>
+        <v>5.317980658543343</v>
       </c>
       <c r="P11" t="n">
-        <v>346.2851474227222</v>
+        <v>346.2591026758584</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28173,28 +28255,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6740867826399261</v>
+        <v>-0.6702909131509986</v>
       </c>
       <c r="J12" t="n">
+        <v>326</v>
+      </c>
+      <c r="K12" t="n">
         <v>325</v>
       </c>
-      <c r="K12" t="n">
-        <v>324</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.4499502114367718</v>
+        <v>0.4477933201430208</v>
       </c>
       <c r="M12" t="n">
-        <v>4.326414304084904</v>
+        <v>4.332847805443882</v>
       </c>
       <c r="N12" t="n">
-        <v>31.0545288539543</v>
+        <v>31.08209053470782</v>
       </c>
       <c r="O12" t="n">
-        <v>5.572659046985945</v>
+        <v>5.575131436541009</v>
       </c>
       <c r="P12" t="n">
-        <v>350.5105168124539</v>
+        <v>350.4700572797154</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28251,28 +28333,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6899536103456857</v>
+        <v>-0.6860753648948783</v>
       </c>
       <c r="J13" t="n">
+        <v>326</v>
+      </c>
+      <c r="K13" t="n">
         <v>325</v>
       </c>
-      <c r="K13" t="n">
-        <v>324</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.4257507846396209</v>
+        <v>0.4237192616612184</v>
       </c>
       <c r="M13" t="n">
-        <v>4.708849955872025</v>
+        <v>4.712545125477602</v>
       </c>
       <c r="N13" t="n">
-        <v>35.89554206235748</v>
+        <v>35.91360981273456</v>
       </c>
       <c r="O13" t="n">
-        <v>5.991288848182625</v>
+        <v>5.992796493519078</v>
       </c>
       <c r="P13" t="n">
-        <v>348.7662183504579</v>
+        <v>348.7248807862337</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28329,28 +28411,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6555881336049917</v>
+        <v>-0.6530973223611656</v>
       </c>
       <c r="J14" t="n">
+        <v>326</v>
+      </c>
+      <c r="K14" t="n">
         <v>325</v>
       </c>
-      <c r="K14" t="n">
-        <v>324</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.4314964609770428</v>
+        <v>0.430822648378964</v>
       </c>
       <c r="M14" t="n">
-        <v>4.348594070795624</v>
+        <v>4.346610909289446</v>
       </c>
       <c r="N14" t="n">
-        <v>31.65730075367773</v>
+        <v>31.61290477313682</v>
       </c>
       <c r="O14" t="n">
-        <v>5.626482093962242</v>
+        <v>5.62253543991826</v>
       </c>
       <c r="P14" t="n">
-        <v>341.7431280931287</v>
+        <v>341.7165789561367</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28407,28 +28489,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6200130406713285</v>
+        <v>-0.6180947681035411</v>
       </c>
       <c r="J15" t="n">
+        <v>326</v>
+      </c>
+      <c r="K15" t="n">
         <v>325</v>
       </c>
-      <c r="K15" t="n">
-        <v>324</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.3968640845365135</v>
+        <v>0.3967160554721634</v>
       </c>
       <c r="M15" t="n">
-        <v>4.553276745572429</v>
+        <v>4.550017598403111</v>
       </c>
       <c r="N15" t="n">
-        <v>32.66110098061243</v>
+        <v>32.59204696959849</v>
       </c>
       <c r="O15" t="n">
-        <v>5.71498914964958</v>
+        <v>5.708944470705464</v>
       </c>
       <c r="P15" t="n">
-        <v>336.5094826178474</v>
+        <v>336.4890360740491</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28485,28 +28567,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5907964015731832</v>
+        <v>-0.5863233931803971</v>
       </c>
       <c r="J16" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K16" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3359495740856483</v>
+        <v>0.333030592119696</v>
       </c>
       <c r="M16" t="n">
-        <v>4.996318479071848</v>
+        <v>5.005204084860642</v>
       </c>
       <c r="N16" t="n">
-        <v>38.80847167563333</v>
+        <v>38.86176654911869</v>
       </c>
       <c r="O16" t="n">
-        <v>6.229644586622364</v>
+        <v>6.233920640264736</v>
       </c>
       <c r="P16" t="n">
-        <v>344.0423961304575</v>
+        <v>343.9949548709098</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28563,28 +28645,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3817000646721397</v>
+        <v>-0.3772001835648608</v>
       </c>
       <c r="J17" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K17" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1777702420084477</v>
+        <v>0.1746073682915443</v>
       </c>
       <c r="M17" t="n">
-        <v>5.000255544070302</v>
+        <v>5.010047887106707</v>
       </c>
       <c r="N17" t="n">
-        <v>37.90552241255494</v>
+        <v>37.96366403161726</v>
       </c>
       <c r="O17" t="n">
-        <v>6.156746089660913</v>
+        <v>6.161466061873363</v>
       </c>
       <c r="P17" t="n">
-        <v>343.2668762429343</v>
+        <v>343.2191499681775</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28641,28 +28723,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.406178720225021</v>
+        <v>-0.4011231403261148</v>
       </c>
       <c r="J18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2235682393793541</v>
+        <v>0.2191993066985664</v>
       </c>
       <c r="M18" t="n">
-        <v>4.623203915837221</v>
+        <v>4.638593054986422</v>
       </c>
       <c r="N18" t="n">
-        <v>32.22933998005598</v>
+        <v>32.35063106870774</v>
       </c>
       <c r="O18" t="n">
-        <v>5.677089041054049</v>
+        <v>5.687761516511372</v>
       </c>
       <c r="P18" t="n">
-        <v>341.3010172919705</v>
+        <v>341.247397209671</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28719,28 +28801,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4748792083829218</v>
+        <v>-0.4694141317287199</v>
       </c>
       <c r="J19" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K19" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3592675843876575</v>
+        <v>0.3528568250058306</v>
       </c>
       <c r="M19" t="n">
-        <v>3.788640697986245</v>
+        <v>3.809416323598367</v>
       </c>
       <c r="N19" t="n">
-        <v>22.62293070447069</v>
+        <v>22.81079820947406</v>
       </c>
       <c r="O19" t="n">
-        <v>4.756356873119456</v>
+        <v>4.77606513873859</v>
       </c>
       <c r="P19" t="n">
-        <v>342.0820328890556</v>
+        <v>342.0240696354168</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28797,28 +28879,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3457133464258273</v>
+        <v>-0.3432399835551086</v>
       </c>
       <c r="J20" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K20" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2410822119682667</v>
+        <v>0.2391985611313676</v>
       </c>
       <c r="M20" t="n">
-        <v>3.729098877163096</v>
+        <v>3.729230328508644</v>
       </c>
       <c r="N20" t="n">
-        <v>21.16341504234908</v>
+        <v>21.15119050849915</v>
       </c>
       <c r="O20" t="n">
-        <v>4.60037118527941</v>
+        <v>4.599042346891268</v>
       </c>
       <c r="P20" t="n">
-        <v>349.2782692482899</v>
+        <v>349.2520364672171</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28875,28 +28957,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.174924516963861</v>
+        <v>-0.1731819400792628</v>
       </c>
       <c r="J21" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K21" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06093749927486625</v>
+        <v>0.0601141038425026</v>
       </c>
       <c r="M21" t="n">
-        <v>3.874712629431413</v>
+        <v>3.874382769098083</v>
       </c>
       <c r="N21" t="n">
-        <v>26.52376244152131</v>
+        <v>26.46855704921724</v>
       </c>
       <c r="O21" t="n">
-        <v>5.150122565679511</v>
+        <v>5.144760154683329</v>
       </c>
       <c r="P21" t="n">
-        <v>350.3537758597204</v>
+        <v>350.3352938818199</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28934,7 +29016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V326"/>
+  <dimension ref="A1:V327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65405,6 +65487,118 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-41.31742715323418,175.8627056190485</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-41.31787884202448,175.8620110162773</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-41.31838541364159,175.86142026449969</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-41.318881836969894,175.8608160670007</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-41.319425864994415,175.86028591979166</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-41.31977213760333,175.85947877020888</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-41.32015833774758,175.85875136126927</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-41.320605893121964,175.85809025307782</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-41.32096175091567,175.85734111590483</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-41.32131615638317,175.8566006737025</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-41.32163362844407,175.85582522690578</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-41.321868148628646,175.85498463585196</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-41.322050232732536,175.85411159602026</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-41.32225441613896,175.85327053179725</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-41.32254182340653,175.85245696606037</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-41.3228366536662,175.8516354240131</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-41.32315819426367,175.85083347536928</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>-41.32351843074655,175.85007548854978</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>-41.32388223225101,175.84931970847313</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>-41.32428915109773,175.8486040175777</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
